--- a/luciferase_data/luciferase_plate_metadata.xlsx
+++ b/luciferase_data/luciferase_plate_metadata.xlsx
@@ -14,7 +14,7 @@
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="1" r:id="rId1"/>
-    <sheet name="Figure 2C" sheetId="2" r:id="rId2"/>
+    <sheet name="Figure 5B" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
